--- a/Seminarios/TablaComparativaConcentrado.xlsx
+++ b/Seminarios/TablaComparativaConcentrado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utrujillo/Documents/Develops/Python/Python3/Vision/analyze_posture_estimation/Seminarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345F484D-B5B6-2147-B712-427705AFEF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A05C58-A0FC-A54B-B5F8-73E7640D3261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29500" yWindow="580" windowWidth="10680" windowHeight="16760" activeTab="1" xr2:uid="{0E2D49C4-014D-F645-895F-A57D6B41FEED}"/>
+    <workbookView xWindow="29500" yWindow="580" windowWidth="11720" windowHeight="16760" activeTab="1" xr2:uid="{0E2D49C4-014D-F645-895F-A57D6B41FEED}"/>
   </bookViews>
   <sheets>
     <sheet name="SIV" sheetId="1" r:id="rId1"/>
@@ -87,19 +87,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFABB2BF"/>
-      <name val="Menlo"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -122,12 +116,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1154,7 +1147,7 @@
       <c r="B20">
         <v>0.1</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20">
         <v>-38.619799999999998</v>
       </c>
     </row>
@@ -1165,7 +1158,7 @@
       <c r="B21">
         <v>0.5</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21">
         <v>-38.628799999999998</v>
       </c>
     </row>
@@ -1176,7 +1169,7 @@
       <c r="B22">
         <v>0.9</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22">
         <v>-38.535899999999998</v>
       </c>
     </row>
@@ -1187,7 +1180,7 @@
       <c r="B23">
         <v>0.1</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23">
         <v>-9.7489999999999993E-2</v>
       </c>
     </row>
@@ -1198,7 +1191,7 @@
       <c r="B24">
         <v>0.5</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24">
         <v>-9.7509999999999999E-2</v>
       </c>
     </row>
@@ -1209,7 +1202,7 @@
       <c r="B25">
         <v>0.9</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25">
         <v>-9.7500000000000003E-2</v>
       </c>
     </row>

--- a/Seminarios/TablaComparativaConcentrado.xlsx
+++ b/Seminarios/TablaComparativaConcentrado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utrujillo/Documents/Develops/Python/Python3/Vision/analyze_posture_estimation/Seminarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A05C58-A0FC-A54B-B5F8-73E7640D3261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660927F0-02D8-1241-8F10-F2CABA6F6CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29500" yWindow="580" windowWidth="11720" windowHeight="16760" activeTab="1" xr2:uid="{0E2D49C4-014D-F645-895F-A57D6B41FEED}"/>
+    <workbookView xWindow="10920" yWindow="740" windowWidth="18480" windowHeight="16760" activeTab="1" xr2:uid="{0E2D49C4-014D-F645-895F-A57D6B41FEED}"/>
   </bookViews>
   <sheets>
     <sheet name="SIV" sheetId="1" r:id="rId1"/>
@@ -924,6 +924,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091CA265-BF89-4542-BBCA-7B2DDC53B74E}">
   <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="13" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
@@ -952,6 +955,15 @@
       <c r="C2">
         <v>95.288499999999999</v>
       </c>
+      <c r="D2">
+        <v>99.1</v>
+      </c>
+      <c r="E2">
+        <v>98.8292</v>
+      </c>
+      <c r="F2">
+        <v>99.650890000000004</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -963,6 +975,15 @@
       <c r="C3">
         <v>100</v>
       </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -972,6 +993,15 @@
         <v>0.9</v>
       </c>
       <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
         <v>100</v>
       </c>
     </row>
@@ -985,6 +1015,15 @@
       <c r="C5">
         <v>0.98699999999999999</v>
       </c>
+      <c r="D5">
+        <v>0.99460000000000004</v>
+      </c>
+      <c r="E5">
+        <v>0.80720000000000003</v>
+      </c>
+      <c r="F5">
+        <v>0.9929</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -996,6 +1035,15 @@
       <c r="C6">
         <v>0.95179999999999998</v>
       </c>
+      <c r="D6">
+        <v>0.9889</v>
+      </c>
+      <c r="E6">
+        <v>0.88580000000000003</v>
+      </c>
+      <c r="F6">
+        <v>0.96709999999999996</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1007,6 +1055,15 @@
       <c r="C7">
         <v>0.71509999999999996</v>
       </c>
+      <c r="D7">
+        <v>0.93259999999999998</v>
+      </c>
+      <c r="E7">
+        <v>0.88649999999999995</v>
+      </c>
+      <c r="F7">
+        <v>0.77890000000000004</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1018,6 +1075,15 @@
       <c r="C8">
         <v>8.8024000000000004</v>
       </c>
+      <c r="D8">
+        <v>4.9526000000000003</v>
+      </c>
+      <c r="E8">
+        <v>6.1559999999999997</v>
+      </c>
+      <c r="F8">
+        <v>4.6475</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1029,6 +1095,15 @@
       <c r="C9">
         <v>8.8024000000000004</v>
       </c>
+      <c r="D9">
+        <v>4.9526000000000003</v>
+      </c>
+      <c r="E9">
+        <v>6.1559999999999997</v>
+      </c>
+      <c r="F9">
+        <v>4.6475</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1040,6 +1115,15 @@
       <c r="C10">
         <v>8.8024000000000004</v>
       </c>
+      <c r="D10">
+        <v>4.9526000000000003</v>
+      </c>
+      <c r="E10">
+        <v>6.1559999999999997</v>
+      </c>
+      <c r="F10">
+        <v>4.6475</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -1051,6 +1135,15 @@
       <c r="C11">
         <v>52.183100000000003</v>
       </c>
+      <c r="D11">
+        <v>48.037700000000001</v>
+      </c>
+      <c r="E11">
+        <v>51.415399999999998</v>
+      </c>
+      <c r="F11">
+        <v>0.34910000000000002</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -1062,6 +1155,15 @@
       <c r="C12">
         <v>2.9529999999999998</v>
       </c>
+      <c r="D12">
+        <v>3.5735999999999999</v>
+      </c>
+      <c r="E12">
+        <v>3.4161000000000001</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -1073,6 +1175,15 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -1084,6 +1195,15 @@
       <c r="C14">
         <v>84.065299999999993</v>
       </c>
+      <c r="D14">
+        <v>250.61</v>
+      </c>
+      <c r="E14">
+        <v>82.215299999999999</v>
+      </c>
+      <c r="F14">
+        <v>1128.835</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -1095,6 +1215,15 @@
       <c r="C15">
         <v>84.295599999999993</v>
       </c>
+      <c r="D15">
+        <v>250.6241</v>
+      </c>
+      <c r="E15">
+        <v>81.968400000000003</v>
+      </c>
+      <c r="F15">
+        <v>1132.3380999999999</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -1106,8 +1235,17 @@
       <c r="C16">
         <v>83.701400000000007</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16">
+        <v>250.61500000000001</v>
+      </c>
+      <c r="E16">
+        <v>82.099000000000004</v>
+      </c>
+      <c r="F16">
+        <v>1134.9820999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1117,8 +1255,17 @@
       <c r="C17">
         <v>13.5589</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17">
+        <v>3.802</v>
+      </c>
+      <c r="E17">
+        <v>12.1409</v>
+      </c>
+      <c r="F17">
+        <v>0.90129999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1128,8 +1275,17 @@
       <c r="C18">
         <v>13.536</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18">
+        <v>3.7928999999999999</v>
+      </c>
+      <c r="E18">
+        <v>12.1431</v>
+      </c>
+      <c r="F18">
+        <v>0.90169999999999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1139,8 +1295,17 @@
       <c r="C19">
         <v>13.558299999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19">
+        <v>3.7917000000000001</v>
+      </c>
+      <c r="E19">
+        <v>12.139699999999999</v>
+      </c>
+      <c r="F19">
+        <v>0.90129999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1150,8 +1315,17 @@
       <c r="C20">
         <v>-38.619799999999998</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20">
+        <v>36.313600000000001</v>
+      </c>
+      <c r="E20">
+        <v>-0.5988</v>
+      </c>
+      <c r="F20">
+        <v>80.438900000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1161,8 +1335,17 @@
       <c r="C21">
         <v>-38.628799999999998</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <v>36.185200000000002</v>
+      </c>
+      <c r="E21">
+        <v>-0.64480000000000004</v>
+      </c>
+      <c r="F21">
+        <v>80.430400000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -1172,8 +1355,17 @@
       <c r="C22">
         <v>-38.535899999999998</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22">
+        <v>35.923200000000001</v>
+      </c>
+      <c r="E22">
+        <v>-0.64380000000000004</v>
+      </c>
+      <c r="F22">
+        <v>80.399299999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -1183,8 +1375,17 @@
       <c r="C23">
         <v>-9.7489999999999993E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <v>0.25080000000000002</v>
+      </c>
+      <c r="E23">
+        <v>1.14E-2</v>
+      </c>
+      <c r="F23">
+        <v>0.62794000000000005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1194,8 +1395,17 @@
       <c r="C24">
         <v>-9.7509999999999999E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D24">
+        <v>0.25330000000000003</v>
+      </c>
+      <c r="E24">
+        <v>1.06E-2</v>
+      </c>
+      <c r="F24">
+        <v>0.56779999999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -1205,8 +1415,17 @@
       <c r="C25">
         <v>-9.7500000000000003E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D25">
+        <v>0.25319999999999998</v>
+      </c>
+      <c r="E25">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="F25">
+        <v>0.5716</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1214,7 +1433,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1222,7 +1441,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>12</v>
       </c>
